--- a/Assets/Game/Content/Data/EffectTable.xlsx
+++ b/Assets/Game/Content/Data/EffectTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NineLivesAtlier\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NineLivesAtlierNew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA0F9143-6A78-4197-8DBC-3F3AEA30AFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BC6075-3922-4B88-8E68-D333C3FAA1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="172">
   <si>
     <t>Id</t>
   </si>
@@ -439,94 +439,94 @@
   </si>
   <si>
     <t>获得坚固</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>获得反射</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>施加反射</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Enemy</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Buff_Stun_Enemy_Desc</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Desc</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Desc</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Enemy_Desc</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Draw_Peace</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Draw_Focus</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>奶</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>集中</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>若上次行动后没有受到伤害则触发</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Focus</t>
   </si>
   <si>
     <t>Focus</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Calm_Peace_Desc</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Draw_Focus_Desc</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Stun_Enemy</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Damage_Focus</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Focus_Desc</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>乘风_伤害</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -539,7 +539,7 @@
       </rPr>
       <t>乘风</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -552,35 +552,92 @@
       </rPr>
       <t>若顺风值大于0则触发</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Damage_Windborne</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>None</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Windborne_Desc</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Windborne</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>集中_抓牌</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>集中_伤害</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Sturdy_Self_Focus</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Reflect_Self_Focus</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Reflect_Self_Focus_Desc</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buff_Sturdy_Self_Focus_Desc</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>集中_坚固</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>集中_反射</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -738,40 +795,40 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -1048,8 +1105,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <dimension ref="A1:I56"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.796875" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
@@ -1060,7 +1117,7 @@
     <col min="9" max="9" width="53.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1074,7 +1131,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1088,7 +1145,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1102,7 +1159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1116,7 +1173,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
@@ -1138,7 +1195,7 @@
       </c>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>19</v>
       </c>
@@ -1162,7 +1219,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>25</v>
       </c>
@@ -1186,7 +1243,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>30</v>
       </c>
@@ -1210,7 +1267,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>36</v>
       </c>
@@ -1234,7 +1291,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>42</v>
       </c>
@@ -1258,7 +1315,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>48</v>
       </c>
@@ -1282,7 +1339,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>51</v>
       </c>
@@ -1306,7 +1363,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>54</v>
       </c>
@@ -1321,7 +1378,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>57</v>
       </c>
@@ -1336,7 +1393,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>60</v>
       </c>
@@ -1351,7 +1408,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>63</v>
       </c>
@@ -1366,7 +1423,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>66</v>
       </c>
@@ -1381,7 +1438,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>69</v>
       </c>
@@ -1396,7 +1453,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>72</v>
       </c>
@@ -1411,7 +1468,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>75</v>
       </c>
@@ -1426,7 +1483,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>78</v>
       </c>
@@ -1441,7 +1498,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>81</v>
       </c>
@@ -1456,7 +1513,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>84</v>
       </c>
@@ -1471,7 +1528,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>87</v>
       </c>
@@ -1486,7 +1543,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>154</v>
       </c>
@@ -1501,7 +1558,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>138</v>
       </c>
@@ -1516,7 +1573,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>139</v>
       </c>
@@ -1531,7 +1588,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>140</v>
       </c>
@@ -1546,7 +1603,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>91</v>
       </c>
@@ -1558,7 +1615,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>93</v>
       </c>
@@ -1570,7 +1627,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>95</v>
       </c>
@@ -1582,7 +1639,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>97</v>
       </c>
@@ -1594,7 +1651,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>99</v>
       </c>
@@ -1606,7 +1663,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>101</v>
       </c>
@@ -1618,7 +1675,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>103</v>
       </c>
@@ -1630,7 +1687,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>105</v>
       </c>
@@ -1642,7 +1699,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>107</v>
       </c>
@@ -1654,7 +1711,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>109</v>
       </c>
@@ -1666,7 +1723,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>133</v>
       </c>
@@ -1678,7 +1735,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>111</v>
       </c>
@@ -1690,7 +1747,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
         <v>113</v>
       </c>
@@ -1702,7 +1759,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>115</v>
       </c>
@@ -1714,7 +1771,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>117</v>
       </c>
@@ -1726,7 +1783,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>119</v>
       </c>
@@ -1738,7 +1795,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>121</v>
       </c>
@@ -1750,7 +1807,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>123</v>
       </c>
@@ -1762,7 +1819,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>125</v>
       </c>
@@ -1774,7 +1831,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>127</v>
       </c>
@@ -1786,7 +1843,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>145</v>
       </c>
@@ -1798,7 +1855,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>130</v>
       </c>
@@ -1810,7 +1867,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>132</v>
       </c>
@@ -1822,7 +1879,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>146</v>
       </c>
@@ -1833,8 +1890,11 @@
       <c r="D52" s="5" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="E52" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>155</v>
       </c>
@@ -1845,29 +1905,62 @@
       <c r="D53" s="5" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="10" t="s">
+      <c r="E53" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B56" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10" t="s">
+      <c r="C56" s="10"/>
+      <c r="D56" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="E54" s="16" t="s">
+      <c r="E56" s="16" t="s">
         <v>157</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D55:D1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D57:D1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$G$5:$G$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D54" xr:uid="{2DEA433D-6731-490A-8B1B-F7BA98B81D90}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D56" xr:uid="{2DEA433D-6731-490A-8B1B-F7BA98B81D90}">
       <formula1>$G$5:$G$11</formula1>
     </dataValidation>
   </dataValidations>

--- a/Assets/Game/Content/Data/EffectTable.xlsx
+++ b/Assets/Game/Content/Data/EffectTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NineLivesAtlierNew\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BC6075-3922-4B88-8E68-D333C3FAA1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5C23BB-AB4A-4CA5-A9CE-AF7E7325ED0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="184">
   <si>
     <t>Id</t>
   </si>
@@ -108,9 +108,6 @@
     <t>涌动：玩家拥有和卡牌属性相同元素的数量不小于阈值时触发</t>
   </si>
   <si>
-    <t>Heal</t>
-  </si>
-  <si>
     <t>Effect_Heal_Desc</t>
   </si>
   <si>
@@ -186,9 +183,6 @@
     <t>中和</t>
   </si>
   <si>
-    <t>Catalyze</t>
-  </si>
-  <si>
     <t>Effect_Catalyze_Desc</t>
   </si>
   <si>
@@ -213,18 +207,12 @@
     <t>加水</t>
   </si>
   <si>
-    <t>Elemental_Earth</t>
-  </si>
-  <si>
     <t>Effect_Elemental_Earth_Desc</t>
   </si>
   <si>
     <t>加气</t>
   </si>
   <si>
-    <t>Elemental_Air</t>
-  </si>
-  <si>
     <t>Effect_Elemental_Air_Desc</t>
   </si>
   <si>
@@ -439,94 +427,94 @@
   </si>
   <si>
     <t>获得坚固</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>获得反射</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>施加反射</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Enemy</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Buff_Stun_Enemy_Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Enemy_Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Draw_Peace</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Draw_Focus</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>奶</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>集中</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>若上次行动后没有受到伤害则触发</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Focus</t>
   </si>
   <si>
     <t>Focus</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Calm_Peace_Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Draw_Focus_Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Stun_Enemy</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Damage_Focus</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Focus_Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>乘风_伤害</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -539,7 +527,7 @@
       </rPr>
       <t>乘风</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -552,23 +540,23 @@
       </rPr>
       <t>若顺风值大于0则触发</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Damage_Windborne</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>None</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Effect_Damage_Windborne_Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Windborne</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -581,7 +569,7 @@
       </rPr>
       <t>集中_抓牌</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -594,50 +582,107 @@
       </rPr>
       <t>集中_伤害</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Focus</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Focus</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Reflect_Self_Focus_Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Buff_Sturdy_Self_Focus_Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>集中_坚固</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>集中_反射</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Draw_Windborne</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Draw_Windborne_Desc</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>乘风_抓牌</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elemental_Earth</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elemental_Air</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elemental_Air_Windborne</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Elemental_Air_Windborne_Desc</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>乘风_加气</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Catalyze</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Catalyze_Windborne</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Catalyze_Windborne_Desc</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>乘风_催化</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heal</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heal_Windborne</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Heal_Windborne_Desc</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>乘风_回血</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -795,44 +840,43 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Good" xfId="1" builtinId="26"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1105,16 +1149,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.796875" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" customWidth="1"/>
-    <col min="4" max="4" width="22.796875" customWidth="1"/>
-    <col min="7" max="7" width="12.296875" customWidth="1"/>
-    <col min="8" max="8" width="8.3984375" customWidth="1"/>
-    <col min="9" max="9" width="53.69921875" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" customWidth="1"/>
+    <col min="9" max="9" width="53.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1221,394 +1265,394 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>26</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="13" t="s">
         <v>28</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>30</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>31</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="H8" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="I8" s="14" t="s">
         <v>34</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>36</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>37</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="I9" s="15" t="s">
         <v>40</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>42</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>43</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="H10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="I10" s="15" t="s">
         <v>46</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>49</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>51</v>
+        <v>176</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>60</v>
+        <v>171</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>63</v>
+        <v>172</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>144</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11" t="s">
@@ -1617,10 +1661,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
@@ -1629,10 +1673,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11" t="s">
@@ -1641,10 +1685,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
@@ -1653,314 +1697,374 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>164</v>
+        <v>146</v>
+      </c>
+      <c r="E52" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>165</v>
+        <v>146</v>
+      </c>
+      <c r="E53" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>170</v>
+        <v>146</v>
+      </c>
+      <c r="E54" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>171</v>
+        <v>146</v>
+      </c>
+      <c r="E55" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="E56" s="16" t="s">
         <v>157</v>
       </c>
+      <c r="E56" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="E57" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="E58" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="E59" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>183</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D57:D1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D61:D1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$G$5:$G$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D56" xr:uid="{2DEA433D-6731-490A-8B1B-F7BA98B81D90}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D60" xr:uid="{2DEA433D-6731-490A-8B1B-F7BA98B81D90}">
       <formula1>$G$5:$G$11</formula1>
     </dataValidation>
   </dataValidations>

--- a/Assets/Game/Content/Data/EffectTable.xlsx
+++ b/Assets/Game/Content/Data/EffectTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLA2.0\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5C23BB-AB4A-4CA5-A9CE-AF7E7325ED0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5EBBB3-EC87-4BDB-9961-FE416FD82E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="6204" yWindow="3804" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -90,9 +90,6 @@
     <t>无条件</t>
   </si>
   <si>
-    <t>Damage_Self</t>
-  </si>
-  <si>
     <t>Effect_Damage_Self_Desc</t>
   </si>
   <si>
@@ -672,12 +669,16 @@
     <t>乘风_回血</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>Damage_Self</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -875,8 +876,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1150,18 +1151,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I60"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" customWidth="1"/>
+    <col min="1" max="1" width="22.796875" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" customWidth="1"/>
-    <col min="4" max="4" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" customWidth="1"/>
-    <col min="9" max="9" width="53.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.19921875" customWidth="1"/>
+    <col min="4" max="4" width="22.796875" customWidth="1"/>
+    <col min="7" max="7" width="12.296875" customWidth="1"/>
+    <col min="8" max="8" width="8.3984375" customWidth="1"/>
+    <col min="9" max="9" width="53.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1175,7 +1176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1189,7 +1190,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1203,7 +1204,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1217,7 +1218,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
@@ -1239,823 +1240,823 @@
       </c>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>20</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="I6" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="13" t="s">
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>25</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="13" t="s">
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="B8" s="10" t="s">
         <v>29</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>30</v>
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="H8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="I8" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="14" t="s">
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="10" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="B9" s="10" t="s">
         <v>35</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>36</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="H9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="I9" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="I9" s="15" t="s">
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="10" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="B10" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>42</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="H10" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="I10" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="I10" s="15" t="s">
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="10" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="B11" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>48</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>50</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="B13" s="10" t="s">
         <v>52</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>53</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="10" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="B14" s="10" t="s">
         <v>55</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>56</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>58</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>60</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="10" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="B17" s="10" t="s">
         <v>62</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>63</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="10" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="B18" s="10" t="s">
         <v>65</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>66</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="10" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="B19" s="10" t="s">
         <v>68</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>69</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="10" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="B20" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>72</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="10" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="B21" s="10" t="s">
         <v>74</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>75</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="10" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="B22" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="B23" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="B24" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>89</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>90</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>92</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>93</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>94</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>106</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" s="10" t="s">
         <v>107</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>108</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>112</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>113</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B48" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B50" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>127</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E52" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E53" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>162</v>
-      </c>
       <c r="B54" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E54" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E55" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E56" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>169</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E57" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B58" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="C58" s="10"/>
       <c r="D58" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E58" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E59" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="B60" s="10" t="s">
         <v>181</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>182</v>
       </c>
       <c r="C60" s="10"/>
       <c r="D60" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Game/Content/Data/EffectTable.xlsx
+++ b/Assets/Game/Content/Data/EffectTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLA2.0\Assets\Game\Content\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E5EBBB3-EC87-4BDB-9961-FE416FD82E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375E2797-AC79-4324-9304-82A4B30BDA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="6204" yWindow="3804" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -279,9 +279,6 @@
     <t>给自己冷静</t>
   </si>
   <si>
-    <t>Buff_Quickness_Self</t>
-  </si>
-  <si>
     <t>Effect_Buff_Quickness_Desc</t>
   </si>
   <si>
@@ -673,12 +670,16 @@
     <t>Damage_Self</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>Buff_Quickness_Self</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -876,8 +877,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Good" xfId="1" builtinId="26"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1151,18 +1152,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I60"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.796875" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="16.19921875" customWidth="1"/>
-    <col min="4" max="4" width="22.796875" customWidth="1"/>
-    <col min="7" max="7" width="12.296875" customWidth="1"/>
-    <col min="8" max="8" width="8.3984375" customWidth="1"/>
-    <col min="9" max="9" width="53.69921875" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" customWidth="1"/>
+    <col min="9" max="9" width="53.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1176,7 +1177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1190,7 +1191,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1204,7 +1205,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1218,7 +1219,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
@@ -1240,9 +1241,9 @@
       </c>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>19</v>
@@ -1264,9 +1265,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>24</v>
@@ -1276,7 +1277,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>25</v>
@@ -1288,7 +1289,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>28</v>
       </c>
@@ -1312,7 +1313,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>34</v>
       </c>
@@ -1336,7 +1337,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>40</v>
       </c>
@@ -1360,7 +1361,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>46</v>
       </c>
@@ -1375,18 +1376,18 @@
         <v>48</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H11" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="I11" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="I11" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>49</v>
@@ -1399,16 +1400,16 @@
         <v>50</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H12" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="I12" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="I12" s="15" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>51</v>
       </c>
@@ -1423,7 +1424,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>54</v>
       </c>
@@ -1438,9 +1439,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>57</v>
@@ -1453,9 +1454,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>59</v>
@@ -1468,7 +1469,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>61</v>
       </c>
@@ -1483,7 +1484,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>64</v>
       </c>
@@ -1498,7 +1499,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>67</v>
       </c>
@@ -1513,7 +1514,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>70</v>
       </c>
@@ -1528,7 +1529,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>73</v>
       </c>
@@ -1543,7 +1544,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>76</v>
       </c>
@@ -1558,7 +1559,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>79</v>
       </c>
@@ -1573,490 +1574,490 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>83</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>88</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>89</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>92</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>93</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>105</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="10" t="s">
         <v>106</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>107</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="10" t="s">
         <v>108</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>109</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>110</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>111</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>112</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>115</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>119</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" s="10" t="s">
         <v>122</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>123</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B50" s="10" t="s">
         <v>125</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>126</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E52" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>151</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E53" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>161</v>
-      </c>
       <c r="B54" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E54" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>163</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E55" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E56" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B57" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>168</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E57" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B58" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>173</v>
       </c>
       <c r="C58" s="10"/>
       <c r="D58" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E58" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" s="10" t="s">
         <v>176</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>177</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E59" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B60" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="C60" s="10"/>
       <c r="D60" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Game/Content/Data/EffectTable.xlsx
+++ b/Assets/Game/Content/Data/EffectTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375E2797-AC79-4324-9304-82A4B30BDA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2C47A8-C4AA-432C-9068-7C3CF3D71B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="196">
   <si>
     <t>Id</t>
   </si>
@@ -202,9 +202,6 @@
   </si>
   <si>
     <t>加水</t>
-  </si>
-  <si>
-    <t>Effect_Elemental_Earth_Desc</t>
   </si>
   <si>
     <t>加气</t>
@@ -541,10 +538,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>None</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Effect_Damage_Windborne_Desc</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -672,6 +665,61 @@
   </si>
   <si>
     <t>Buff_Quickness_Self</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Elemental_Earth_Desc</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Windborne</t>
+  </si>
+  <si>
+    <t>Aftermath</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>余响</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>被献祭时触发</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>余响_伤害</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage_Aftermath</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Draw_Aftermath</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heal_Aftermath</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Draw_Aftermath_Desc</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Heal_Aftermath_Desc</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>余响_抓牌</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>余响_治疗</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect_Damage_Aftermath_Desc</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -846,7 +894,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -875,6 +923,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1151,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.77734375" customWidth="1"/>
@@ -1243,7 +1292,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>19</v>
@@ -1267,7 +1316,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>24</v>
@@ -1277,7 +1326,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>25</v>
@@ -1376,18 +1425,18 @@
         <v>48</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H11" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="I11" s="15" t="s">
         <v>142</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>49</v>
@@ -1400,13 +1449,13 @@
         <v>50</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H12" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I12" s="15" t="s">
         <v>152</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1423,6 +1472,15 @@
       <c r="E13" t="s">
         <v>53</v>
       </c>
+      <c r="G13" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
@@ -1441,220 +1499,220 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>57</v>
+        <v>182</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>61</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>62</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>64</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>65</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>68</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>74</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>76</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>77</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>86</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11" t="s">
@@ -1663,10 +1721,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
@@ -1675,10 +1733,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>89</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>90</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11" t="s">
@@ -1687,10 +1745,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>91</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>92</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
@@ -1699,10 +1757,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>94</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5" t="s">
@@ -1711,10 +1769,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>96</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5" t="s">
@@ -1723,10 +1781,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5" t="s">
@@ -1735,10 +1793,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5" t="s">
@@ -1747,10 +1805,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5" t="s">
@@ -1759,10 +1817,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5" t="s">
@@ -1771,10 +1829,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5" t="s">
@@ -1783,10 +1841,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B40" s="10" t="s">
         <v>105</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>106</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10" t="s">
@@ -1795,10 +1853,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" s="10" t="s">
         <v>107</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>108</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10" t="s">
@@ -1807,10 +1865,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>109</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>110</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" s="10" t="s">
@@ -1819,10 +1877,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>111</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>112</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10" t="s">
@@ -1831,10 +1889,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5" t="s">
@@ -1843,10 +1901,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5" t="s">
@@ -1855,10 +1913,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5" t="s">
@@ -1867,10 +1925,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="5" t="s">
@@ -1879,10 +1937,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>122</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="10" t="s">
@@ -1891,10 +1949,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="10" t="s">
@@ -1903,10 +1961,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>125</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="10" t="s">
@@ -1915,10 +1973,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10" t="s">
@@ -1927,143 +1985,188 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E52" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>150</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E53" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E54" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E55" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B56" s="10" t="s">
         <v>154</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="E56" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="10" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="E57" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C58" s="10"/>
       <c r="D58" s="10" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="E58" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="10" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="E59" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C60" s="10"/>
       <c r="D60" s="10" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E61" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D61:D1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D64:D1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$G$5:$G$10</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D60" xr:uid="{2DEA433D-6731-490A-8B1B-F7BA98B81D90}">

--- a/Assets/Game/Content/Data/EffectTable.xlsx
+++ b/Assets/Game/Content/Data/EffectTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProj\NLANew\Assets\Game\Content\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2C47A8-C4AA-432C-9068-7C3CF3D71B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830D9325-27B7-4747-B48D-C6A890193E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -171,9 +171,6 @@
     <t>若没有手牌则触发</t>
   </si>
   <si>
-    <t>Neutralize</t>
-  </si>
-  <si>
     <t>Effect_Neutralize_Desc</t>
   </si>
   <si>
@@ -720,6 +717,10 @@
   </si>
   <si>
     <t>Effect_Damage_Aftermath_Desc</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Neutralize</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1292,7 +1293,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>19</v>
@@ -1316,7 +1317,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>24</v>
@@ -1326,7 +1327,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>25</v>
@@ -1412,307 +1413,307 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="10" t="s">
         <v>46</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>47</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H11" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" s="15" t="s">
         <v>141</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H12" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I12" s="15" t="s">
         <v>151</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G13" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="I13" s="16" t="s">
         <v>185</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>60</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>61</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>63</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>64</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>66</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>67</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>70</v>
       </c>
       <c r="C20" s="10"/>
       <c r="D20" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>72</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>73</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>79</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>84</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>85</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11" t="s">
@@ -1721,10 +1722,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11" t="s">
@@ -1733,10 +1734,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="10" t="s">
         <v>88</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>89</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11" t="s">
@@ -1745,10 +1746,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11" t="s">
@@ -1757,10 +1758,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5" t="s">
@@ -1769,10 +1770,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5" t="s">
@@ -1781,10 +1782,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5" t="s">
@@ -1793,10 +1794,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5" t="s">
@@ -1805,10 +1806,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5" t="s">
@@ -1817,10 +1818,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>103</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5" t="s">
@@ -1829,10 +1830,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5" t="s">
@@ -1841,10 +1842,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="10" t="s">
         <v>104</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>105</v>
       </c>
       <c r="C40" s="10"/>
       <c r="D40" s="10" t="s">
@@ -1853,10 +1854,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B41" s="10" t="s">
         <v>106</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>107</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="10" t="s">
@@ -1865,10 +1866,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>108</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>109</v>
       </c>
       <c r="C42" s="10"/>
       <c r="D42" s="10" t="s">
@@ -1877,10 +1878,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>110</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>111</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="10" t="s">
@@ -1889,10 +1890,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5" t="s">
@@ -1901,10 +1902,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>115</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5" t="s">
@@ -1913,10 +1914,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5" t="s">
@@ -1925,10 +1926,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>119</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="5" t="s">
@@ -1937,10 +1938,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" s="10" t="s">
         <v>120</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>121</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="10" t="s">
@@ -1949,10 +1950,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="10" t="s">
@@ -1961,10 +1962,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B50" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>124</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="10" t="s">
@@ -1973,10 +1974,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10" t="s">
@@ -1985,182 +1986,182 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E52" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E53" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E54" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B56" s="10" t="s">
         <v>153</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>154</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E56" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B57" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>165</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E57" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B58" s="10" t="s">
         <v>169</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>170</v>
       </c>
       <c r="C58" s="10"/>
       <c r="D58" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E58" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B59" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E59" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B60" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="C60" s="10"/>
       <c r="D60" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E61" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
